--- a/file/qs-30.xlsx
+++ b/file/qs-30.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B34"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -431,396 +431,288 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>300920</t>
+          <t>002355</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>润阳科技</t>
+          <t>兴民智通</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>001234</t>
+          <t>002549</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>泰慕士</t>
+          <t>凯美特气</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>603101</t>
+          <t>000677</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>汇嘉时代</t>
+          <t>恒天海龙</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>600249</t>
+          <t>603086</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>两面针</t>
+          <t>先达股份</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>001331</t>
+          <t>002427</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>胜通能源</t>
+          <t>尤夫股份</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>003001</t>
+          <t>600105</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>中岩大地</t>
+          <t>永鼎股份</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>603057</t>
+          <t>600589</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>紫燕食品</t>
+          <t>大位科技</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>603137</t>
+          <t>600203</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>恒尚节能</t>
+          <t>福日电子</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>603237</t>
+          <t>603030</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>五芳斋</t>
+          <t>全筑股份</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>002661</t>
+          <t>601908</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>克明食品</t>
+          <t>京运通</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>600865</t>
+          <t>002122</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>百大集团</t>
+          <t>汇洲智能</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>601033</t>
+          <t>002512</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>永兴股份</t>
+          <t>达华智能</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>001328</t>
+          <t>000903</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>登康口腔</t>
+          <t>云内动力</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>603886</t>
+          <t>002440</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>元祖股份</t>
+          <t>闰土股份</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>002852</t>
+          <t>600396</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>道道全</t>
+          <t>华电辽能</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>300908</t>
+          <t>600503</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>仲景食品</t>
+          <t>华丽家族</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>603193</t>
+          <t>001896</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>润本股份</t>
+          <t>豫能控股</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>001219</t>
+          <t>002482</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>青岛食品</t>
+          <t>广田集团</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>002584</t>
+          <t>002094</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>西陇科学</t>
+          <t>青岛金王</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>002040</t>
+          <t>002639</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>南 京 港</t>
+          <t>雪人股份</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>601083</t>
+          <t>002255</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>锦江航运</t>
+          <t>海陆重工</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>603182</t>
+          <t>002471</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>嘉华股份</t>
+          <t>中超控股</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>600573</t>
+          <t>600744</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>惠泉啤酒</t>
+          <t>华银电力</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>300281</t>
+          <t>603169</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>金明精机</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>603266</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>天龙股份</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>603214</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>爱婴室</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>300858</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>科拓生物</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>301092</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>争光股份</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>600785</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>新华百货</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>603329</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>上海雅仕</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>603648</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>畅联股份</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>002772</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>众兴菌业</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>301066</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>万事利</t>
+          <t>兰石重装</t>
         </is>
       </c>
     </row>
